--- a/data/GreatLink/Income Bond_Dividends.xlsx
+++ b/data/GreatLink/Income Bond_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid786099"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid161672"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
-  </si>
-  <si>
-    <t>0.003</t>
   </si>
   <si>
     <t>03/12/2025</t>
@@ -565,18 +568,18 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +590,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -598,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -609,7 +612,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +623,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -873,18 +876,18 @@
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -939,7 +942,7 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -950,7 +953,7 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -961,7 +964,7 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -972,7 +975,7 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
@@ -983,7 +986,7 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
@@ -994,7 +997,7 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -1005,18 +1008,18 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
         <v>49</v>
-      </c>
-      <c r="B44" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1104,7 +1107,7 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -1115,7 +1118,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54">
@@ -1126,7 +1129,7 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
@@ -1137,7 +1140,7 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
@@ -1148,7 +1151,7 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -1159,7 +1162,7 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
@@ -1170,7 +1173,7 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
@@ -1181,7 +1184,18 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/GreatLink/Income Bond_Dividends.xlsx
+++ b/data/GreatLink/Income Bond_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid161672"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid187803"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
     <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>0.003</t>
   </si>
   <si>
     <t>06/01/2026</t>
@@ -579,18 +582,18 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -601,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +626,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -634,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -887,18 +890,18 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
@@ -953,7 +956,7 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -964,7 +967,7 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -975,7 +978,7 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -986,7 +989,7 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
@@ -997,7 +1000,7 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
@@ -1008,7 +1011,7 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -1019,18 +1022,18 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
         <v>50</v>
-      </c>
-      <c r="B45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1118,7 +1121,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1129,7 +1132,7 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55">
@@ -1140,7 +1143,7 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
@@ -1151,7 +1154,7 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
@@ -1162,7 +1165,7 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
@@ -1173,7 +1176,7 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1187,7 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
@@ -1195,7 +1198,18 @@
         <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
